--- a/characteristics_tables/COVID_Study_Characteristics.xlsx
+++ b/characteristics_tables/COVID_Study_Characteristics.xlsx
@@ -2367,12 +2367,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Non-randomized single arm</t>
+          <t>Observational - with comparator group</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>case series/report</t>
+          <t>SCCS (self-controlled case series)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2443,12 +2443,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical: D1: Confounding</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Observational - with comparator group</t>
+          <t>Non-randomized single arm</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>case-control</t>
+          <t>only 1 arm eligible, treated as single arm</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Mean (SD): Mean (SD): 36.48 ± 0.232</t>
+          <t>NR</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -7596,17 +7596,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2534</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Observational - with comparator group</t>
+          <t>Non-randomized single arm</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>prospective cohort</t>
+          <t>only 1 arm eligible, treated as single arm</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Other OUS postmarketing registry: Department of Pharmacology at Bangabandhu Sheikh Mujib Medical University (BSMMU)</t>
+          <t>Department of Pharmacology at Bangabandhu Sheikh Mujib Medical University (BSMMU)</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -7646,27 +7646,12 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>Grant committee of Bangabandhu Sheikh Mujib Medical University (BSMMU). University research grant Fund. Memo no. 2021-2022/02.</t>
+          <t>This study was supported by the grant committee of Bangabandhu Sheikh Mujib Medical University (BSMMU). University research grant Fund. Memo no. 2021-2022/02</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
           <t>Scientific Reports</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>41006405</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>PMC12475045</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12475045/</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
@@ -8211,12 +8196,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Non-randomized single arm</t>
+          <t>Observational - with comparator group</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>only 1 arm eligible, treated as single arm</t>
+          <t>retrospective cohort</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -13920,7 +13905,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>Safety: Other SAEs per study defn, Other SAEs per study defn: Death</t>
+          <t>Safety: Other SAEs per study defn: Death</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -24442,7 +24427,7 @@
         </is>
       </c>
       <c r="D58">
-        <v>2534</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="59">
@@ -36463,7 +36448,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -36481,7 +36471,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -36499,7 +36494,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -36517,7 +36517,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -36535,7 +36540,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -36553,7 +36563,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -36571,7 +36586,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -36589,7 +36609,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -36607,7 +36632,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>

--- a/characteristics_tables/COVID_Study_Characteristics.xlsx
+++ b/characteristics_tables/COVID_Study_Characteristics.xlsx
@@ -961,7 +961,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Critical: D1: Confounding</t>
+          <t>Critical: D1: Confounding; Critical: awaiting domain decision</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Serious: D1: Confounding</t>
+          <t>Critical: D1: Confounding</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>Serious</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>Critical: awaiting domain decision</t>
+          <t>Not Assessed Due to Study Design: awaiting domain decision</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Not Assessed Due to Study Design</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Effectiveness: Disease-related hospitalization or ED visits</t>
+          <t>Effectiveness: Lab-confirmed infection or illness</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical: awaiting domain decision</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -7233,12 +7233,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>High: D1: Randomization; High: D2: Deviations from the intended interventions</t>
+          <t>Some Concerns: D1: Randomization; Some Concerns: D2: Deviations from the intended interventions</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Some Concerns</t>
         </is>
       </c>
     </row>
@@ -12944,7 +12944,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>vanDijk 2025</t>
+          <t>VanDijk 2025</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13022,16 +13022,6 @@
           <t>Safety: Thrombosis</t>
         </is>
       </c>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>Safety: Thrombosis</t>
-        </is>
-      </c>
-      <c r="R104" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
       <c r="S104" t="inlineStr">
         <is>
           <t>Dutch Ministry of Health, Welfare and Sport (reference number 333053)</t>
@@ -13064,12 +13054,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>Critical: D1: Confounding</t>
+          <t>No risk of bias data in outcomes sheet</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>No risk of bias data in outcomes sheet</t>
         </is>
       </c>
     </row>
@@ -14605,7 +14595,7 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>Critical: D1: Confounding</t>
+          <t>Critical: D1: Confounding; Critical: awaiting domain decision</t>
         </is>
       </c>
       <c r="Z117" t="inlineStr">
@@ -14874,7 +14864,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>vanBeek 2025</t>
+          <t>VanBeek 2025</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14942,16 +14932,6 @@
           <t>Safety: Serious adverse events (SAEs)</t>
         </is>
       </c>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>Safety: Serious adverse events (SAEs)</t>
-        </is>
-      </c>
-      <c r="R120" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
       <c r="S120" t="inlineStr">
         <is>
           <t>The European Regional Development Fund (ERDF), REACT-EU: HVaNa project, PROJ-01113. Funder had no role in study design, in the collection, analysis and interpretation of data, in the writing of the report, and in the decision to submit the article for publication.</t>
@@ -14979,12 +14959,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>Critical: awaiting domain decision</t>
+          <t>No risk of bias data in outcomes sheet</t>
         </is>
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>No risk of bias data in outcomes sheet</t>
         </is>
       </c>
     </row>
@@ -15353,12 +15333,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical: awaiting domain decision</t>
         </is>
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -15963,12 +15943,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Not Assessed Due to Study Design: awaiting domain decision</t>
         </is>
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Not Assessed Due to Study Design</t>
         </is>
       </c>
     </row>
@@ -16076,12 +16056,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Not Assessed Due to Study Design: awaiting domain decision</t>
         </is>
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Not Assessed Due to Study Design</t>
         </is>
       </c>
     </row>
@@ -16317,12 +16297,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Not Assessed Due to Study Design: awaiting domain decision</t>
         </is>
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Not Assessed Due to Study Design</t>
         </is>
       </c>
     </row>
@@ -16671,12 +16651,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Not Assessed Due to Study Design: awaiting domain decision</t>
         </is>
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Not Assessed Due to Study Design</t>
         </is>
       </c>
     </row>
@@ -17173,12 +17153,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Not Assessed Due to Study Design: awaiting domain decision</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Not Assessed Due to Study Design</t>
         </is>
       </c>
     </row>
@@ -17419,12 +17399,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical: awaiting domain decision</t>
         </is>
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -17537,12 +17517,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Not Assessed Due to Study Design: awaiting domain decision</t>
         </is>
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Not Assessed Due to Study Design</t>
         </is>
       </c>
     </row>
@@ -17655,12 +17635,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Not Assessed Due to Study Design: awaiting domain decision</t>
         </is>
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Not Assessed Due to Study Design</t>
         </is>
       </c>
     </row>
@@ -17783,12 +17763,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Serious: awaiting domain decision</t>
         </is>
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Serious</t>
         </is>
       </c>
     </row>
@@ -17907,12 +17887,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>High: awaiting domain decision</t>
         </is>
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -18035,12 +18015,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -18158,12 +18138,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Moderate: awaiting domain decision</t>
         </is>
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -18286,12 +18266,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Serious: awaiting domain decision</t>
         </is>
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Serious</t>
         </is>
       </c>
     </row>
@@ -18399,12 +18379,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Not Assessed Due to Study Design: awaiting domain decision</t>
         </is>
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Not Assessed Due to Study Design</t>
         </is>
       </c>
     </row>
@@ -18522,12 +18502,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -18645,12 +18625,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Serious: awaiting domain decision</t>
         </is>
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Serious</t>
         </is>
       </c>
     </row>
@@ -18768,12 +18748,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Moderate: awaiting domain decision</t>
         </is>
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -18896,12 +18876,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Serious: awaiting domain decision</t>
         </is>
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Serious</t>
         </is>
       </c>
     </row>
@@ -19019,12 +18999,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Moderate: awaiting domain decision</t>
         </is>
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>Assessment in Progress</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -24475,7 +24455,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>vanDijk 2025</t>
+          <t>VanDijk 2025</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25257,7 +25237,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>vanBeek 2025</t>
+          <t>VanBeek 2025</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -28285,7 +28265,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>vanDijk 2025</t>
+          <t>VanDijk 2025</t>
         </is>
       </c>
       <c r="D103">
@@ -28541,7 +28521,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>vanBeek 2025</t>
+          <t>VanBeek 2025</t>
         </is>
       </c>
       <c r="D119">
@@ -33251,7 +33231,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>vanDijk 2025</t>
+          <t>VanDijk 2025</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -33269,7 +33249,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>vanDijk 2025</t>
+          <t>VanDijk 2025</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -33827,7 +33807,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>vanBeek 2025</t>
+          <t>VanBeek 2025</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -37279,7 +37259,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>vanDijk 2025</t>
+          <t>VanDijk 2025</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -37567,7 +37547,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>vanBeek 2025</t>
+          <t>VanBeek 2025</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -38339,7 +38319,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E554"/>
+  <dimension ref="A1:E459"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -39268,14 +39248,14 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="B41">
-        <v>1183</v>
+        <v>703</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Parker 2025</t>
+          <t>Toepfer 2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -39475,14 +39455,14 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B50">
-        <v>1257</v>
+        <v>1183</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Silk 2026</t>
+          <t>Parker 2025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -39751,14 +39731,14 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="B62">
-        <v>1905</v>
+        <v>1257</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Munjal 2025</t>
+          <t>Silk 2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -39774,14 +39754,14 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B63">
-        <v>1924</v>
+        <v>1905</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Soe 2025</t>
+          <t>Munjal 2025</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -39958,14 +39938,14 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B71">
-        <v>1970</v>
+        <v>1924</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Wei 2025</t>
+          <t>Soe 2025</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -40027,14 +40007,14 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B74">
-        <v>2150</v>
+        <v>1970</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Grubber 2026</t>
+          <t>Wei 2025</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -40303,14 +40283,14 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="B86">
-        <v>21459</v>
+        <v>2150</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Carazo 2026</t>
+          <t>Grubber 2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -40441,14 +40421,14 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B92">
-        <v>21461</v>
+        <v>21459</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dadhe 2026</t>
+          <t>Carazo 2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -40602,19 +40582,19 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B99">
-        <v>21487</v>
+        <v>21461</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>BergstadLarsen 2026</t>
+          <t>Dadhe 2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Serious</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -40637,7 +40617,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Serious</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -40660,7 +40640,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Serious</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -40683,7 +40663,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Serious</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -40706,7 +40686,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Serious</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -40729,7 +40709,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Serious</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -40752,7 +40732,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Serious</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -40775,7 +40755,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Serious</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -40798,7 +40778,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Serious</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -40821,7 +40801,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Serious</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -40832,24 +40812,24 @@
     </row>
     <row r="109">
       <c r="A109">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B109">
-        <v>21517</v>
+        <v>21487</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Oyedele 2026</t>
+          <t>BergstadLarsen 2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>D1: Randomization</t>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -40918,25 +40898,30 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>D2: Deviations from the intended interventions</t>
+          <t>D1: Randomization</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B113">
-        <v>21534</v>
+        <v>21517</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Govender 2026</t>
+          <t>Oyedele 2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
@@ -40960,24 +40945,19 @@
     </row>
     <row r="115">
       <c r="A115">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B115">
-        <v>21612</v>
+        <v>21534</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Madley-Dowd 2026</t>
+          <t>Govender 2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Serious</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>D1: Confounding</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -41144,19 +41124,19 @@
     </row>
     <row r="123">
       <c r="A123">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B123">
-        <v>21613</v>
+        <v>21612</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Asomaning 2026</t>
+          <t>Madley-Dowd 2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Serious</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -41351,24 +41331,24 @@
     </row>
     <row r="132">
       <c r="A132">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B132">
-        <v>21621</v>
+        <v>21613</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Vicic 2026</t>
+          <t>Asomaning 2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Serious</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>D2: Classification of Interventions</t>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -41460,7 +41440,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>D3: Selection of participants</t>
+          <t>D2: Classification of Interventions</t>
         </is>
       </c>
     </row>
@@ -41552,7 +41532,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>D5: Measurement of the outcome</t>
+          <t>D3: Selection of participants</t>
         </is>
       </c>
     </row>
@@ -41627,24 +41607,24 @@
     </row>
     <row r="144">
       <c r="A144">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B144">
-        <v>21634</v>
+        <v>21621</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Schmetz 2026</t>
+          <t>Vicic 2026</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Serious</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D5: Measurement of the outcome</t>
         </is>
       </c>
     </row>
@@ -41719,14 +41699,14 @@
     </row>
     <row r="148">
       <c r="A148">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B148">
-        <v>21649</v>
+        <v>21634</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Ma 2026</t>
+          <t>Schmetz 2026</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -41765,14 +41745,14 @@
     </row>
     <row r="150">
       <c r="A150">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B150">
-        <v>21664</v>
+        <v>21649</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Oliveira 2026</t>
+          <t>Ma 2026</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -41949,14 +41929,14 @@
     </row>
     <row r="158">
       <c r="A158">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B158">
-        <v>21738</v>
+        <v>21664</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Chappell 2026</t>
+          <t>Oliveira 2026</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -42110,14 +42090,14 @@
     </row>
     <row r="165">
       <c r="A165">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B165">
-        <v>21791</v>
+        <v>21738</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Separovic 2026</t>
+          <t>Chappell 2026</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -42156,14 +42136,14 @@
     </row>
     <row r="167">
       <c r="A167">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B167">
-        <v>21815</v>
+        <v>21791</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Correcher-Martinez 2026</t>
+          <t>Separovic 2026</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -42363,19 +42343,24 @@
     </row>
     <row r="176">
       <c r="A176">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B176">
-        <v>21854</v>
+        <v>21815</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Obeidat 2026</t>
+          <t>Correcher-Martinez 2026</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -43413,7 +43398,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Some Concerns</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -43436,7 +43421,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Some Concerns</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -43459,7 +43444,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Some Concerns</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -46026,37 +46011,37 @@
     </row>
     <row r="337">
       <c r="A337">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B337">
-        <v>25922</v>
+        <v>26331</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>vanDijk 2025</t>
+          <t>Stemler 2026</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D1: Randomization</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B338">
-        <v>25922</v>
+        <v>26591</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>vanDijk 2025</t>
+          <t>Soff 2026</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -46072,14 +46057,14 @@
     </row>
     <row r="339">
       <c r="A339">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B339">
-        <v>25922</v>
+        <v>26591</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>vanDijk 2025</t>
+          <t>Soff 2026</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -46095,14 +46080,14 @@
     </row>
     <row r="340">
       <c r="A340">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B340">
-        <v>25922</v>
+        <v>26591</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>vanDijk 2025</t>
+          <t>Soff 2026</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -46118,19 +46103,19 @@
     </row>
     <row r="341">
       <c r="A341">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B341">
-        <v>25922</v>
+        <v>26774</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>vanDijk 2025</t>
+          <t>Volkman 2026</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -46141,19 +46126,19 @@
     </row>
     <row r="342">
       <c r="A342">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B342">
-        <v>25922</v>
+        <v>26774</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>vanDijk 2025</t>
+          <t>Volkman 2026</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -46164,19 +46149,19 @@
     </row>
     <row r="343">
       <c r="A343">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B343">
-        <v>25922</v>
+        <v>26774</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>vanDijk 2025</t>
+          <t>Volkman 2026</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -46187,83 +46172,83 @@
     </row>
     <row r="344">
       <c r="A344">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B344">
-        <v>25922</v>
+        <v>26774</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>vanDijk 2025</t>
+          <t>Volkman 2026</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D3: Selection of participants</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B345">
-        <v>25922</v>
+        <v>26774</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>vanDijk 2025</t>
+          <t>Volkman 2026</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D3: Selection of participants</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B346">
-        <v>25922</v>
+        <v>26774</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>vanDijk 2025</t>
+          <t>Volkman 2026</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D3: Selection of participants</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="B347">
-        <v>25922</v>
+        <v>27423</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>vanDijk 2025</t>
+          <t>Azar 2025</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -46279,19 +46264,19 @@
     </row>
     <row r="348">
       <c r="A348">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="B348">
-        <v>25922</v>
+        <v>27778</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>vanDijk 2025</t>
+          <t>Andersen 2025</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Serious</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -46302,19 +46287,19 @@
     </row>
     <row r="349">
       <c r="A349">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="B349">
-        <v>25922</v>
+        <v>27778</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>vanDijk 2025</t>
+          <t>Andersen 2025</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Serious</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -46325,60 +46310,60 @@
     </row>
     <row r="350">
       <c r="A350">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="B350">
-        <v>25922</v>
+        <v>27778</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>vanDijk 2025</t>
+          <t>Andersen 2025</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Serious</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D3: Selection of participants</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="B351">
-        <v>25922</v>
+        <v>27778</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>vanDijk 2025</t>
+          <t>Andersen 2025</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Serious</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D3: Selection of participants</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="B352">
-        <v>25922</v>
+        <v>29322</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>vanDijk 2025</t>
+          <t>Benist 2026</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -46394,14 +46379,14 @@
     </row>
     <row r="353">
       <c r="A353">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="B353">
-        <v>25922</v>
+        <v>29322</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>vanDijk 2025</t>
+          <t>Benist 2026</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -46417,19 +46402,19 @@
     </row>
     <row r="354">
       <c r="A354">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="B354">
-        <v>25922</v>
+        <v>29396</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>vanDijk 2025</t>
+          <t>Hernan 2026</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -46440,42 +46425,42 @@
     </row>
     <row r="355">
       <c r="A355">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="B355">
-        <v>26331</v>
+        <v>29396</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Stemler 2026</t>
+          <t>Hernan 2026</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>D1: Randomization</t>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="B356">
-        <v>26591</v>
+        <v>29396</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Soff 2026</t>
+          <t>Hernan 2026</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -46486,19 +46471,19 @@
     </row>
     <row r="357">
       <c r="A357">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="B357">
-        <v>26591</v>
+        <v>29396</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Soff 2026</t>
+          <t>Hernan 2026</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -46509,19 +46494,19 @@
     </row>
     <row r="358">
       <c r="A358">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="B358">
-        <v>26591</v>
+        <v>29396</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Soff 2026</t>
+          <t>Hernan 2026</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -46532,14 +46517,14 @@
     </row>
     <row r="359">
       <c r="A359">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B359">
-        <v>26774</v>
+        <v>29396</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Volkman 2026</t>
+          <t>Hernan 2026</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -46555,14 +46540,14 @@
     </row>
     <row r="360">
       <c r="A360">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B360">
-        <v>26774</v>
+        <v>29396</v>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Volkman 2026</t>
+          <t>Hernan 2026</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -46572,20 +46557,20 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D3: Selection of participants</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B361">
-        <v>26774</v>
+        <v>29396</v>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Volkman 2026</t>
+          <t>Hernan 2026</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -46595,20 +46580,20 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D3: Selection of participants</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B362">
-        <v>26774</v>
+        <v>29396</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Volkman 2026</t>
+          <t>Hernan 2026</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -46618,20 +46603,20 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D3: Selection of participants</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B363">
-        <v>26774</v>
+        <v>29396</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Volkman 2026</t>
+          <t>Hernan 2026</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -46647,14 +46632,14 @@
     </row>
     <row r="364">
       <c r="A364">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B364">
-        <v>26774</v>
+        <v>29396</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Volkman 2026</t>
+          <t>Hernan 2026</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -46670,14 +46655,14 @@
     </row>
     <row r="365">
       <c r="A365">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B365">
-        <v>26774</v>
+        <v>29396</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Volkman 2026</t>
+          <t>Hernan 2026</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -46693,152 +46678,152 @@
     </row>
     <row r="366">
       <c r="A366">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="B366">
-        <v>26774</v>
+        <v>31021</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Volkman 2026</t>
+          <t>Mackay 2025</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>D3: Selection of participants</t>
+          <t>D1: Randomization</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="B367">
-        <v>27423</v>
+        <v>31021</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Azar 2025</t>
+          <t>Mackay 2025</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D1: Randomization</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B368">
-        <v>27778</v>
+        <v>31021</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Andersen 2025</t>
+          <t>Mackay 2025</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Serious</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D1: Randomization</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B369">
-        <v>27778</v>
+        <v>31021</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Andersen 2025</t>
+          <t>Mackay 2025</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Serious</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D1: Randomization</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B370">
-        <v>27778</v>
+        <v>31021</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Andersen 2025</t>
+          <t>Mackay 2025</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Serious</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>D3: Selection of participants</t>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="B371">
-        <v>27778</v>
+        <v>32102</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Andersen 2025</t>
+          <t>Alby-Laurent 2026</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Serious</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>D3: Selection of participants</t>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="B372">
-        <v>29322</v>
+        <v>32102</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Benist 2026</t>
+          <t>Alby-Laurent 2026</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -46854,14 +46839,14 @@
     </row>
     <row r="373">
       <c r="A373">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="B373">
-        <v>29322</v>
+        <v>32469</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Benist 2026</t>
+          <t>Lobo-Martins 2026</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -46877,19 +46862,19 @@
     </row>
     <row r="374">
       <c r="A374">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="B374">
-        <v>29396</v>
+        <v>32469</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Hernan 2026</t>
+          <t>Lobo-Martins 2026</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -46900,19 +46885,19 @@
     </row>
     <row r="375">
       <c r="A375">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="B375">
-        <v>29396</v>
+        <v>32469</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Hernan 2026</t>
+          <t>Lobo-Martins 2026</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -46923,19 +46908,19 @@
     </row>
     <row r="376">
       <c r="A376">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="B376">
-        <v>29396</v>
+        <v>32537</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Hernan 2026</t>
+          <t>DiCecca 2026</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -46946,19 +46931,19 @@
     </row>
     <row r="377">
       <c r="A377">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="B377">
-        <v>29396</v>
+        <v>32537</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Hernan 2026</t>
+          <t>DiCecca 2026</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -46969,19 +46954,19 @@
     </row>
     <row r="378">
       <c r="A378">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="B378">
-        <v>29396</v>
+        <v>32537</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Hernan 2026</t>
+          <t>DiCecca 2026</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -46992,19 +46977,19 @@
     </row>
     <row r="379">
       <c r="A379">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B379">
-        <v>29396</v>
+        <v>32641</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Hernan 2026</t>
+          <t>Song 2026</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -47015,972 +47000,872 @@
     </row>
     <row r="380">
       <c r="A380">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B380">
-        <v>29396</v>
+        <v>32641</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Hernan 2026</t>
+          <t>Song 2026</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>D3: Selection of participants</t>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B381">
-        <v>29396</v>
+        <v>32641</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Hernan 2026</t>
+          <t>Song 2026</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>D3: Selection of participants</t>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B382">
-        <v>29396</v>
+        <v>32641</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Hernan 2026</t>
+          <t>Song 2026</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>D3: Selection of participants</t>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B383">
-        <v>29396</v>
+        <v>32641</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Hernan 2026</t>
+          <t>Song 2026</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>D3: Selection of participants</t>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="B384">
-        <v>29396</v>
+        <v>32806</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Hernan 2026</t>
+          <t>Pfeiffer 2026</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>D3: Selection of participants</t>
+          <t>D1: Randomization</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="B385">
-        <v>29396</v>
+        <v>32935</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Hernan 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="E385" t="inlineStr">
-        <is>
-          <t>D3: Selection of participants</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="B386">
-        <v>31021</v>
+        <v>32935</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Mackay 2025</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E386" t="inlineStr">
-        <is>
-          <t>D1: Randomization</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="B387">
-        <v>31021</v>
+        <v>32935</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Mackay 2025</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E387" t="inlineStr">
-        <is>
-          <t>D1: Randomization</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="B388">
-        <v>31021</v>
+        <v>32935</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Mackay 2025</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E388" t="inlineStr">
-        <is>
-          <t>D1: Randomization</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="B389">
-        <v>31021</v>
+        <v>32935</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Mackay 2025</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E389" t="inlineStr">
-        <is>
-          <t>D1: Randomization</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="B390">
-        <v>31021</v>
+        <v>32935</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Mackay 2025</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E390" t="inlineStr">
-        <is>
-          <t>D2: Deviations from the intended interventions</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="B391">
-        <v>31265</v>
+        <v>32935</v>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>He 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="B392">
-        <v>31265</v>
+        <v>32935</v>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>He 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="B393">
-        <v>31265</v>
+        <v>32935</v>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>He 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="B394">
-        <v>31265</v>
+        <v>32935</v>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>He 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="B395">
-        <v>31265</v>
+        <v>32935</v>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>He 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="B396">
-        <v>31265</v>
+        <v>32935</v>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>He 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="B397">
-        <v>32102</v>
+        <v>32935</v>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Alby-Laurent 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E397" t="inlineStr">
-        <is>
-          <t>D1: Confounding</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="B398">
-        <v>32102</v>
+        <v>32935</v>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Alby-Laurent 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E398" t="inlineStr">
-        <is>
-          <t>D1: Confounding</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="B399">
-        <v>32436</v>
+        <v>32935</v>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Cintron 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="B400">
-        <v>32457</v>
+        <v>32935</v>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Aslam 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B401">
-        <v>32469</v>
+        <v>32935</v>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Lobo-Martins 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E401" t="inlineStr">
-        <is>
-          <t>D1: Confounding</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B402">
-        <v>32469</v>
+        <v>32935</v>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Lobo-Martins 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E402" t="inlineStr">
-        <is>
-          <t>D1: Confounding</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B403">
-        <v>32469</v>
+        <v>32935</v>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Lobo-Martins 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E403" t="inlineStr">
-        <is>
-          <t>D1: Confounding</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B404">
-        <v>32494</v>
+        <v>32935</v>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Hamid 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B405">
-        <v>32494</v>
+        <v>32935</v>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Hamid 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B406">
-        <v>32494</v>
+        <v>32935</v>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Hamid 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B407">
-        <v>32494</v>
+        <v>32935</v>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Hamid 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B408">
-        <v>32494</v>
+        <v>32935</v>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Hamid 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B409">
-        <v>32494</v>
+        <v>32935</v>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Hamid 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B410">
-        <v>32494</v>
+        <v>32935</v>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Hamid 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B411">
-        <v>32494</v>
+        <v>32935</v>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Hamid 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B412">
-        <v>32494</v>
+        <v>32935</v>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Hamid 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B413">
-        <v>32494</v>
+        <v>32935</v>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Hamid 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B414">
-        <v>32494</v>
+        <v>32935</v>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Hamid 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B415">
-        <v>32494</v>
+        <v>32935</v>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Hamid 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B416">
-        <v>32533</v>
+        <v>32935</v>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Kehl-Floberg 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B417">
-        <v>32537</v>
+        <v>32935</v>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>DiCecca 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E417" t="inlineStr">
-        <is>
-          <t>D1: Confounding</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B418">
-        <v>32537</v>
+        <v>32935</v>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>DiCecca 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E418" t="inlineStr">
-        <is>
-          <t>D1: Confounding</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B419">
-        <v>32537</v>
+        <v>32935</v>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>DiCecca 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E419" t="inlineStr">
-        <is>
-          <t>D1: Confounding</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B420">
-        <v>32641</v>
+        <v>32935</v>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Song 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E420" t="inlineStr">
-        <is>
-          <t>D1: Confounding</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B421">
-        <v>32641</v>
+        <v>32935</v>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Song 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E421" t="inlineStr">
-        <is>
-          <t>D1: Confounding</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B422">
-        <v>32641</v>
+        <v>32935</v>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Song 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E422" t="inlineStr">
-        <is>
-          <t>D1: Confounding</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B423">
-        <v>32641</v>
+        <v>32935</v>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Song 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E423" t="inlineStr">
-        <is>
-          <t>D1: Confounding</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B424">
-        <v>32641</v>
+        <v>32935</v>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Song 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E424" t="inlineStr">
-        <is>
-          <t>D1: Confounding</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B425">
-        <v>32806</v>
+        <v>32935</v>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Pfeiffer 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E425" t="inlineStr">
-        <is>
-          <t>D1: Randomization</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B426">
-        <v>32875</v>
+        <v>32935</v>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>He 2026</t>
+          <t>Xie 2026</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>assessment in progress</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -48526,14 +48411,14 @@
     </row>
     <row r="457">
       <c r="A457">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B457">
-        <v>32935</v>
+        <v>32983</v>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Xie 2026</t>
+          <t>Cai 2026</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -48544,14 +48429,14 @@
     </row>
     <row r="458">
       <c r="A458">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B458">
-        <v>32935</v>
+        <v>32983</v>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Xie 2026</t>
+          <t>Cai 2026</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -48562,1729 +48447,19 @@
     </row>
     <row r="459">
       <c r="A459">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="B459">
-        <v>32935</v>
+        <v>33058</v>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Xie 2026</t>
+          <t>Harris 2026</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460">
-        <v>271</v>
-      </c>
-      <c r="B460">
-        <v>32935</v>
-      </c>
-      <c r="C460" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D460" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461">
-        <v>271</v>
-      </c>
-      <c r="B461">
-        <v>32935</v>
-      </c>
-      <c r="C461" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D461" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462">
-        <v>271</v>
-      </c>
-      <c r="B462">
-        <v>32935</v>
-      </c>
-      <c r="C462" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D462" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463">
-        <v>271</v>
-      </c>
-      <c r="B463">
-        <v>32935</v>
-      </c>
-      <c r="C463" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D463" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464">
-        <v>271</v>
-      </c>
-      <c r="B464">
-        <v>32935</v>
-      </c>
-      <c r="C464" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D464" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465">
-        <v>271</v>
-      </c>
-      <c r="B465">
-        <v>32935</v>
-      </c>
-      <c r="C465" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D465" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="466">
-      <c r="A466">
-        <v>271</v>
-      </c>
-      <c r="B466">
-        <v>32935</v>
-      </c>
-      <c r="C466" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D466" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="467">
-      <c r="A467">
-        <v>271</v>
-      </c>
-      <c r="B467">
-        <v>32935</v>
-      </c>
-      <c r="C467" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D467" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468">
-        <v>271</v>
-      </c>
-      <c r="B468">
-        <v>32935</v>
-      </c>
-      <c r="C468" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D468" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="469">
-      <c r="A469">
-        <v>271</v>
-      </c>
-      <c r="B469">
-        <v>32935</v>
-      </c>
-      <c r="C469" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D469" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470">
-        <v>271</v>
-      </c>
-      <c r="B470">
-        <v>32935</v>
-      </c>
-      <c r="C470" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D470" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471">
-        <v>271</v>
-      </c>
-      <c r="B471">
-        <v>32935</v>
-      </c>
-      <c r="C471" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D471" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472">
-        <v>271</v>
-      </c>
-      <c r="B472">
-        <v>32935</v>
-      </c>
-      <c r="C472" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D472" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473">
-        <v>271</v>
-      </c>
-      <c r="B473">
-        <v>32935</v>
-      </c>
-      <c r="C473" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="474">
-      <c r="A474">
-        <v>271</v>
-      </c>
-      <c r="B474">
-        <v>32935</v>
-      </c>
-      <c r="C474" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D474" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="475">
-      <c r="A475">
-        <v>271</v>
-      </c>
-      <c r="B475">
-        <v>32935</v>
-      </c>
-      <c r="C475" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476">
-        <v>271</v>
-      </c>
-      <c r="B476">
-        <v>32935</v>
-      </c>
-      <c r="C476" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D476" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477">
-        <v>271</v>
-      </c>
-      <c r="B477">
-        <v>32935</v>
-      </c>
-      <c r="C477" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D477" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478">
-        <v>271</v>
-      </c>
-      <c r="B478">
-        <v>32935</v>
-      </c>
-      <c r="C478" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479">
-        <v>271</v>
-      </c>
-      <c r="B479">
-        <v>32935</v>
-      </c>
-      <c r="C479" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480">
-        <v>271</v>
-      </c>
-      <c r="B480">
-        <v>32935</v>
-      </c>
-      <c r="C480" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D480" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="481">
-      <c r="A481">
-        <v>271</v>
-      </c>
-      <c r="B481">
-        <v>32935</v>
-      </c>
-      <c r="C481" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482">
-        <v>271</v>
-      </c>
-      <c r="B482">
-        <v>32935</v>
-      </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D482" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483">
-        <v>271</v>
-      </c>
-      <c r="B483">
-        <v>32935</v>
-      </c>
-      <c r="C483" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D483" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484">
-        <v>271</v>
-      </c>
-      <c r="B484">
-        <v>32935</v>
-      </c>
-      <c r="C484" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D484" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485">
-        <v>271</v>
-      </c>
-      <c r="B485">
-        <v>32935</v>
-      </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D485" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486">
-        <v>271</v>
-      </c>
-      <c r="B486">
-        <v>32935</v>
-      </c>
-      <c r="C486" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D486" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487">
-        <v>271</v>
-      </c>
-      <c r="B487">
-        <v>32935</v>
-      </c>
-      <c r="C487" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D487" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488">
-        <v>271</v>
-      </c>
-      <c r="B488">
-        <v>32935</v>
-      </c>
-      <c r="C488" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D488" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="489">
-      <c r="A489">
-        <v>271</v>
-      </c>
-      <c r="B489">
-        <v>32935</v>
-      </c>
-      <c r="C489" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D489" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="490">
-      <c r="A490">
-        <v>271</v>
-      </c>
-      <c r="B490">
-        <v>32935</v>
-      </c>
-      <c r="C490" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D490" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491">
-        <v>271</v>
-      </c>
-      <c r="B491">
-        <v>32935</v>
-      </c>
-      <c r="C491" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D491" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="492">
-      <c r="A492">
-        <v>271</v>
-      </c>
-      <c r="B492">
-        <v>32935</v>
-      </c>
-      <c r="C492" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D492" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="493">
-      <c r="A493">
-        <v>271</v>
-      </c>
-      <c r="B493">
-        <v>32935</v>
-      </c>
-      <c r="C493" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D493" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="494">
-      <c r="A494">
-        <v>271</v>
-      </c>
-      <c r="B494">
-        <v>32935</v>
-      </c>
-      <c r="C494" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D494" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="495">
-      <c r="A495">
-        <v>271</v>
-      </c>
-      <c r="B495">
-        <v>32935</v>
-      </c>
-      <c r="C495" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D495" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="496">
-      <c r="A496">
-        <v>271</v>
-      </c>
-      <c r="B496">
-        <v>32935</v>
-      </c>
-      <c r="C496" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D496" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="497">
-      <c r="A497">
-        <v>271</v>
-      </c>
-      <c r="B497">
-        <v>32935</v>
-      </c>
-      <c r="C497" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D497" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498">
-        <v>271</v>
-      </c>
-      <c r="B498">
-        <v>32935</v>
-      </c>
-      <c r="C498" t="inlineStr">
-        <is>
-          <t>Xie 2026</t>
-        </is>
-      </c>
-      <c r="D498" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="499">
-      <c r="A499">
-        <v>272</v>
-      </c>
-      <c r="B499">
-        <v>32936</v>
-      </c>
-      <c r="C499" t="inlineStr">
-        <is>
-          <t>Myers 2026</t>
-        </is>
-      </c>
-      <c r="D499" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="500">
-      <c r="A500">
-        <v>273</v>
-      </c>
-      <c r="B500">
-        <v>32937</v>
-      </c>
-      <c r="C500" t="inlineStr">
-        <is>
-          <t>Espenhain 2026</t>
-        </is>
-      </c>
-      <c r="D500" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="501">
-      <c r="A501">
-        <v>273</v>
-      </c>
-      <c r="B501">
-        <v>32937</v>
-      </c>
-      <c r="C501" t="inlineStr">
-        <is>
-          <t>Espenhain 2026</t>
-        </is>
-      </c>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="502">
-      <c r="A502">
-        <v>274</v>
-      </c>
-      <c r="B502">
-        <v>32949</v>
-      </c>
-      <c r="C502" t="inlineStr">
-        <is>
-          <t>Anghelina 2026</t>
-        </is>
-      </c>
-      <c r="D502" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="503">
-      <c r="A503">
-        <v>274</v>
-      </c>
-      <c r="B503">
-        <v>32949</v>
-      </c>
-      <c r="C503" t="inlineStr">
-        <is>
-          <t>Anghelina 2026</t>
-        </is>
-      </c>
-      <c r="D503" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="504">
-      <c r="A504">
-        <v>274</v>
-      </c>
-      <c r="B504">
-        <v>32949</v>
-      </c>
-      <c r="C504" t="inlineStr">
-        <is>
-          <t>Anghelina 2026</t>
-        </is>
-      </c>
-      <c r="D504" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="505">
-      <c r="A505">
-        <v>275</v>
-      </c>
-      <c r="B505">
-        <v>32951</v>
-      </c>
-      <c r="C505" t="inlineStr">
-        <is>
-          <t>Appaneal 2026</t>
-        </is>
-      </c>
-      <c r="D505" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="506">
-      <c r="A506">
-        <v>276</v>
-      </c>
-      <c r="B506">
-        <v>32973</v>
-      </c>
-      <c r="C506" t="inlineStr">
-        <is>
-          <t>Bonten 2026</t>
-        </is>
-      </c>
-      <c r="D506" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="507">
-      <c r="A507">
-        <v>276</v>
-      </c>
-      <c r="B507">
-        <v>32973</v>
-      </c>
-      <c r="C507" t="inlineStr">
-        <is>
-          <t>Bonten 2026</t>
-        </is>
-      </c>
-      <c r="D507" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="508">
-      <c r="A508">
-        <v>277</v>
-      </c>
-      <c r="B508">
-        <v>32983</v>
-      </c>
-      <c r="C508" t="inlineStr">
-        <is>
-          <t>Cai 2026</t>
-        </is>
-      </c>
-      <c r="D508" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="509">
-      <c r="A509">
-        <v>277</v>
-      </c>
-      <c r="B509">
-        <v>32983</v>
-      </c>
-      <c r="C509" t="inlineStr">
-        <is>
-          <t>Cai 2026</t>
-        </is>
-      </c>
-      <c r="D509" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="510">
-      <c r="A510">
-        <v>278</v>
-      </c>
-      <c r="B510">
-        <v>32988</v>
-      </c>
-      <c r="C510" t="inlineStr">
-        <is>
-          <t>Carazo 2026</t>
-        </is>
-      </c>
-      <c r="D510" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="511">
-      <c r="A511">
-        <v>279</v>
-      </c>
-      <c r="B511">
-        <v>32995</v>
-      </c>
-      <c r="C511" t="inlineStr">
-        <is>
-          <t>Chen 2026</t>
-        </is>
-      </c>
-      <c r="D511" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="512">
-      <c r="A512">
-        <v>279</v>
-      </c>
-      <c r="B512">
-        <v>32995</v>
-      </c>
-      <c r="C512" t="inlineStr">
-        <is>
-          <t>Chen 2026</t>
-        </is>
-      </c>
-      <c r="D512" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="513">
-      <c r="A513">
-        <v>280</v>
-      </c>
-      <c r="B513">
-        <v>32999</v>
-      </c>
-      <c r="C513" t="inlineStr">
-        <is>
-          <t>Chopak-Foss 2026</t>
-        </is>
-      </c>
-      <c r="D513" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="514">
-      <c r="A514">
-        <v>280</v>
-      </c>
-      <c r="B514">
-        <v>32999</v>
-      </c>
-      <c r="C514" t="inlineStr">
-        <is>
-          <t>Chopak-Foss 2026</t>
-        </is>
-      </c>
-      <c r="D514" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="515">
-      <c r="A515">
-        <v>280</v>
-      </c>
-      <c r="B515">
-        <v>32999</v>
-      </c>
-      <c r="C515" t="inlineStr">
-        <is>
-          <t>Chopak-Foss 2026</t>
-        </is>
-      </c>
-      <c r="D515" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="516">
-      <c r="A516">
-        <v>280</v>
-      </c>
-      <c r="B516">
-        <v>32999</v>
-      </c>
-      <c r="C516" t="inlineStr">
-        <is>
-          <t>Chopak-Foss 2026</t>
-        </is>
-      </c>
-      <c r="D516" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517">
-        <v>280</v>
-      </c>
-      <c r="B517">
-        <v>32999</v>
-      </c>
-      <c r="C517" t="inlineStr">
-        <is>
-          <t>Chopak-Foss 2026</t>
-        </is>
-      </c>
-      <c r="D517" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="518">
-      <c r="A518">
-        <v>280</v>
-      </c>
-      <c r="B518">
-        <v>32999</v>
-      </c>
-      <c r="C518" t="inlineStr">
-        <is>
-          <t>Chopak-Foss 2026</t>
-        </is>
-      </c>
-      <c r="D518" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="519">
-      <c r="A519">
-        <v>280</v>
-      </c>
-      <c r="B519">
-        <v>32999</v>
-      </c>
-      <c r="C519" t="inlineStr">
-        <is>
-          <t>Chopak-Foss 2026</t>
-        </is>
-      </c>
-      <c r="D519" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="520">
-      <c r="A520">
-        <v>280</v>
-      </c>
-      <c r="B520">
-        <v>32999</v>
-      </c>
-      <c r="C520" t="inlineStr">
-        <is>
-          <t>Chopak-Foss 2026</t>
-        </is>
-      </c>
-      <c r="D520" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521">
-        <v>280</v>
-      </c>
-      <c r="B521">
-        <v>32999</v>
-      </c>
-      <c r="C521" t="inlineStr">
-        <is>
-          <t>Chopak-Foss 2026</t>
-        </is>
-      </c>
-      <c r="D521" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="522">
-      <c r="A522">
-        <v>280</v>
-      </c>
-      <c r="B522">
-        <v>32999</v>
-      </c>
-      <c r="C522" t="inlineStr">
-        <is>
-          <t>Chopak-Foss 2026</t>
-        </is>
-      </c>
-      <c r="D522" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="523">
-      <c r="A523">
-        <v>280</v>
-      </c>
-      <c r="B523">
-        <v>32999</v>
-      </c>
-      <c r="C523" t="inlineStr">
-        <is>
-          <t>Chopak-Foss 2026</t>
-        </is>
-      </c>
-      <c r="D523" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="524">
-      <c r="A524">
-        <v>280</v>
-      </c>
-      <c r="B524">
-        <v>32999</v>
-      </c>
-      <c r="C524" t="inlineStr">
-        <is>
-          <t>Chopak-Foss 2026</t>
-        </is>
-      </c>
-      <c r="D524" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="525">
-      <c r="A525">
-        <v>280</v>
-      </c>
-      <c r="B525">
-        <v>32999</v>
-      </c>
-      <c r="C525" t="inlineStr">
-        <is>
-          <t>Chopak-Foss 2026</t>
-        </is>
-      </c>
-      <c r="D525" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="526">
-      <c r="A526">
-        <v>280</v>
-      </c>
-      <c r="B526">
-        <v>32999</v>
-      </c>
-      <c r="C526" t="inlineStr">
-        <is>
-          <t>Chopak-Foss 2026</t>
-        </is>
-      </c>
-      <c r="D526" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="527">
-      <c r="A527">
-        <v>280</v>
-      </c>
-      <c r="B527">
-        <v>32999</v>
-      </c>
-      <c r="C527" t="inlineStr">
-        <is>
-          <t>Chopak-Foss 2026</t>
-        </is>
-      </c>
-      <c r="D527" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="528">
-      <c r="A528">
-        <v>280</v>
-      </c>
-      <c r="B528">
-        <v>32999</v>
-      </c>
-      <c r="C528" t="inlineStr">
-        <is>
-          <t>Chopak-Foss 2026</t>
-        </is>
-      </c>
-      <c r="D528" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="529">
-      <c r="A529">
-        <v>280</v>
-      </c>
-      <c r="B529">
-        <v>32999</v>
-      </c>
-      <c r="C529" t="inlineStr">
-        <is>
-          <t>Chopak-Foss 2026</t>
-        </is>
-      </c>
-      <c r="D529" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="530">
-      <c r="A530">
-        <v>280</v>
-      </c>
-      <c r="B530">
-        <v>32999</v>
-      </c>
-      <c r="C530" t="inlineStr">
-        <is>
-          <t>Chopak-Foss 2026</t>
-        </is>
-      </c>
-      <c r="D530" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="531">
-      <c r="A531">
-        <v>280</v>
-      </c>
-      <c r="B531">
-        <v>32999</v>
-      </c>
-      <c r="C531" t="inlineStr">
-        <is>
-          <t>Chopak-Foss 2026</t>
-        </is>
-      </c>
-      <c r="D531" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="532">
-      <c r="A532">
-        <v>280</v>
-      </c>
-      <c r="B532">
-        <v>32999</v>
-      </c>
-      <c r="C532" t="inlineStr">
-        <is>
-          <t>Chopak-Foss 2026</t>
-        </is>
-      </c>
-      <c r="D532" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="533">
-      <c r="A533">
-        <v>280</v>
-      </c>
-      <c r="B533">
-        <v>32999</v>
-      </c>
-      <c r="C533" t="inlineStr">
-        <is>
-          <t>Chopak-Foss 2026</t>
-        </is>
-      </c>
-      <c r="D533" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="534">
-      <c r="A534">
-        <v>280</v>
-      </c>
-      <c r="B534">
-        <v>32999</v>
-      </c>
-      <c r="C534" t="inlineStr">
-        <is>
-          <t>Chopak-Foss 2026</t>
-        </is>
-      </c>
-      <c r="D534" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="535">
-      <c r="A535">
-        <v>280</v>
-      </c>
-      <c r="B535">
-        <v>32999</v>
-      </c>
-      <c r="C535" t="inlineStr">
-        <is>
-          <t>Chopak-Foss 2026</t>
-        </is>
-      </c>
-      <c r="D535" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="536">
-      <c r="A536">
-        <v>280</v>
-      </c>
-      <c r="B536">
-        <v>32999</v>
-      </c>
-      <c r="C536" t="inlineStr">
-        <is>
-          <t>Chopak-Foss 2026</t>
-        </is>
-      </c>
-      <c r="D536" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="537">
-      <c r="A537">
-        <v>281</v>
-      </c>
-      <c r="B537">
-        <v>33058</v>
-      </c>
-      <c r="C537" t="inlineStr">
-        <is>
-          <t>Harris 2026</t>
-        </is>
-      </c>
-      <c r="D537" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="538">
-      <c r="A538">
-        <v>282</v>
-      </c>
-      <c r="B538">
-        <v>33166</v>
-      </c>
-      <c r="C538" t="inlineStr">
-        <is>
-          <t>Perumal 2026</t>
-        </is>
-      </c>
-      <c r="D538" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="539">
-      <c r="A539">
-        <v>283</v>
-      </c>
-      <c r="B539">
-        <v>33245</v>
-      </c>
-      <c r="C539" t="inlineStr">
-        <is>
-          <t>Vicic 2026</t>
-        </is>
-      </c>
-      <c r="D539" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="540">
-      <c r="A540">
-        <v>283</v>
-      </c>
-      <c r="B540">
-        <v>33245</v>
-      </c>
-      <c r="C540" t="inlineStr">
-        <is>
-          <t>Vicic 2026</t>
-        </is>
-      </c>
-      <c r="D540" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="541">
-      <c r="A541">
-        <v>283</v>
-      </c>
-      <c r="B541">
-        <v>33245</v>
-      </c>
-      <c r="C541" t="inlineStr">
-        <is>
-          <t>Vicic 2026</t>
-        </is>
-      </c>
-      <c r="D541" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="542">
-      <c r="A542">
-        <v>283</v>
-      </c>
-      <c r="B542">
-        <v>33245</v>
-      </c>
-      <c r="C542" t="inlineStr">
-        <is>
-          <t>Vicic 2026</t>
-        </is>
-      </c>
-      <c r="D542" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="543">
-      <c r="A543">
-        <v>283</v>
-      </c>
-      <c r="B543">
-        <v>33245</v>
-      </c>
-      <c r="C543" t="inlineStr">
-        <is>
-          <t>Vicic 2026</t>
-        </is>
-      </c>
-      <c r="D543" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="544">
-      <c r="A544">
-        <v>283</v>
-      </c>
-      <c r="B544">
-        <v>33245</v>
-      </c>
-      <c r="C544" t="inlineStr">
-        <is>
-          <t>Vicic 2026</t>
-        </is>
-      </c>
-      <c r="D544" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="545">
-      <c r="A545">
-        <v>283</v>
-      </c>
-      <c r="B545">
-        <v>33245</v>
-      </c>
-      <c r="C545" t="inlineStr">
-        <is>
-          <t>Vicic 2026</t>
-        </is>
-      </c>
-      <c r="D545" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="546">
-      <c r="A546">
-        <v>283</v>
-      </c>
-      <c r="B546">
-        <v>33245</v>
-      </c>
-      <c r="C546" t="inlineStr">
-        <is>
-          <t>Vicic 2026</t>
-        </is>
-      </c>
-      <c r="D546" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="547">
-      <c r="A547">
-        <v>284</v>
-      </c>
-      <c r="B547">
-        <v>33255</v>
-      </c>
-      <c r="C547" t="inlineStr">
-        <is>
-          <t>Wiegand 2026</t>
-        </is>
-      </c>
-      <c r="D547" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="548">
-      <c r="A548">
-        <v>284</v>
-      </c>
-      <c r="B548">
-        <v>33255</v>
-      </c>
-      <c r="C548" t="inlineStr">
-        <is>
-          <t>Wiegand 2026</t>
-        </is>
-      </c>
-      <c r="D548" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="549">
-      <c r="A549">
-        <v>284</v>
-      </c>
-      <c r="B549">
-        <v>33255</v>
-      </c>
-      <c r="C549" t="inlineStr">
-        <is>
-          <t>Wiegand 2026</t>
-        </is>
-      </c>
-      <c r="D549" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="550">
-      <c r="A550">
-        <v>284</v>
-      </c>
-      <c r="B550">
-        <v>33255</v>
-      </c>
-      <c r="C550" t="inlineStr">
-        <is>
-          <t>Wiegand 2026</t>
-        </is>
-      </c>
-      <c r="D550" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="551">
-      <c r="A551">
-        <v>285</v>
-      </c>
-      <c r="B551">
-        <v>33257</v>
-      </c>
-      <c r="C551" t="inlineStr">
-        <is>
-          <t>Wilson 2026</t>
-        </is>
-      </c>
-      <c r="D551" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="552">
-      <c r="A552">
-        <v>285</v>
-      </c>
-      <c r="B552">
-        <v>33257</v>
-      </c>
-      <c r="C552" t="inlineStr">
-        <is>
-          <t>Wilson 2026</t>
-        </is>
-      </c>
-      <c r="D552" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="553">
-      <c r="A553">
-        <v>285</v>
-      </c>
-      <c r="B553">
-        <v>33257</v>
-      </c>
-      <c r="C553" t="inlineStr">
-        <is>
-          <t>Wilson 2026</t>
-        </is>
-      </c>
-      <c r="D553" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="554">
-      <c r="A554">
-        <v>285</v>
-      </c>
-      <c r="B554">
-        <v>33257</v>
-      </c>
-      <c r="C554" t="inlineStr">
-        <is>
-          <t>Wilson 2026</t>
-        </is>
-      </c>
-      <c r="D554" t="inlineStr">
-        <is>
-          <t>assessment in progress</t>
         </is>
       </c>
     </row>
